--- a/Plotting/Latex/filtered_data_sensitivity_import.xlsx
+++ b/Plotting/Latex/filtered_data_sensitivity_import.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,19 +472,25 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Brownfield (Scope 1, 2, and 3)</t>
-        </is>
-      </c>
+      <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Brownfield (Scope 1, 2, and 3)</t>
+        </is>
+      </c>
       <c r="N1" s="1" t="n"/>
       <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="n"/>
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,25 +514,39 @@
       <c r="I2" s="1" t="n"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Direct Emissions from MPW Gasification</t>
+          <t>No \ce{CO2} electrolyzers</t>
         </is>
       </c>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Optimistic Bio-Feedstock Prices</t>
+          <t>Direct Emissions from MPW Gasification</t>
         </is>
       </c>
       <c r="N2" s="1" t="n"/>
       <c r="O2" s="1" t="n"/>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>Tighter Short-Term Emission Limit</t>
+          <t>Optimistic Bio-Feedstock Prices</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n"/>
       <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>No \ce{CO2} electrolyzers</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="n"/>
+      <c r="U2" s="1" t="n"/>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>Tighter Short-Term Emission Limit</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="n"/>
+      <c r="X2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -617,6 +637,36 @@
           <t>Long-term</t>
         </is>
       </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>Mid-term</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="V3" s="1" t="inlineStr">
+        <is>
+          <t>Short-term</t>
+        </is>
+      </c>
+      <c r="W3" s="1" t="inlineStr">
+        <is>
+          <t>Mid-term</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -675,6 +725,24 @@
         <v>2000</v>
       </c>
       <c r="R5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>750</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2441</v>
+      </c>
+      <c r="V5" t="n">
+        <v>750</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X5" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -711,30 +779,48 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="L6" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>105</v>
       </c>
       <c r="N6" t="n">
+        <v>45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>105</v>
+      </c>
+      <c r="P6" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q6" t="n">
         <v>108</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>107</v>
+      </c>
+      <c r="T6" t="n">
         <v>114</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="U6" t="n">
+        <v>83</v>
+      </c>
+      <c r="V6" t="n">
         <v>114</v>
       </c>
-      <c r="R6" t="n">
+      <c r="W6" t="n">
+        <v>114</v>
+      </c>
+      <c r="X6" t="n">
         <v>148</v>
       </c>
     </row>
@@ -771,30 +857,48 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>172</v>
+        <v>338</v>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="M7" t="n">
         <v>172</v>
       </c>
       <c r="N7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>172</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>172</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>338</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>338</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>338</v>
+      </c>
+      <c r="V7" t="n">
+        <v>338</v>
+      </c>
+      <c r="W7" t="n">
+        <v>338</v>
+      </c>
+      <c r="X7" t="n">
         <v>338</v>
       </c>
     </row>
@@ -831,30 +935,48 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1066</v>
+        <v>803</v>
       </c>
       <c r="K8" t="n">
-        <v>1092</v>
+        <v>70</v>
       </c>
       <c r="L8" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>1066</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="P8" t="n">
+        <v>1066</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>853</v>
+      </c>
+      <c r="T8" t="n">
+        <v>827</v>
+      </c>
+      <c r="U8" t="n">
+        <v>758</v>
+      </c>
+      <c r="V8" t="n">
         <v>845</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="W8" t="n">
         <v>746</v>
       </c>
-      <c r="R8" t="n">
+      <c r="X8" t="n">
         <v>746</v>
       </c>
     </row>
@@ -897,24 +1019,42 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>751</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1066</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>1067</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,24 +1097,42 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>56</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>75</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,13 +1169,13 @@
         <v>157</v>
       </c>
       <c r="J11" t="n">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="K11" t="n">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>157</v>
@@ -1029,26 +1187,46 @@
         <v>157</v>
       </c>
       <c r="P11" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>157</v>
+      </c>
+      <c r="R11" t="n">
+        <v>157</v>
+      </c>
+      <c r="S11" t="n">
         <v>64</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>64</v>
+      </c>
+      <c r="U11" t="n">
+        <v>64</v>
+      </c>
+      <c r="V11" t="n">
+        <v>64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="D1:L1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="M1:X1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="V2:X2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Plotting/Latex/filtered_data_sensitivity_import.xlsx
+++ b/Plotting/Latex/filtered_data_sensitivity_import.xlsx
@@ -734,7 +734,7 @@
         <v>2000</v>
       </c>
       <c r="U5" t="n">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="V5" t="n">
         <v>750</v>
@@ -764,16 +764,16 @@
         <v>109</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -788,16 +788,16 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="n">
         <v>108</v>
@@ -920,7 +920,7 @@
         <v>1089</v>
       </c>
       <c r="E8" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -938,22 +938,22 @@
         <v>803</v>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N8" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O8" t="n">
         <v>162</v>
       </c>
       <c r="P8" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -962,22 +962,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="T8" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="U8" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="V8" t="n">
         <v>845</v>
       </c>
       <c r="W8" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="X8" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="9">
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="I9" t="n">
         <v>738</v>
@@ -1034,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="R9" t="n">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>157</v>
       </c>
       <c r="F11" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G11" t="n">
         <v>157</v>
@@ -1172,7 +1172,7 @@
         <v>64</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
